--- a/artfynd/A 7126-2026 artfynd.xlsx
+++ b/artfynd/A 7126-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128794507</v>
+        <v>128794525</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510771</v>
+        <v>510696</v>
       </c>
       <c r="R2" t="n">
-        <v>7106380</v>
+        <v>7106461</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128794508</v>
+        <v>128794498</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510782</v>
+        <v>510780</v>
       </c>
       <c r="R3" t="n">
-        <v>7106356</v>
+        <v>7106391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128794492</v>
+        <v>128794509</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510773</v>
+        <v>510663</v>
       </c>
       <c r="R4" t="n">
-        <v>7106391</v>
+        <v>7106445</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -945,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -976,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128794519</v>
+        <v>128794478</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>511436</v>
+        <v>511159</v>
       </c>
       <c r="R5" t="n">
-        <v>7106614</v>
+        <v>7106615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1078,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128794520</v>
+        <v>128794479</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1089,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>511309</v>
+        <v>510847</v>
       </c>
       <c r="R6" t="n">
-        <v>7106636</v>
+        <v>7106602</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128794499</v>
+        <v>128794480</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1186,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>511149</v>
+        <v>510843</v>
       </c>
       <c r="R7" t="n">
-        <v>7106300</v>
+        <v>7106605</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128794477</v>
+        <v>128794481</v>
       </c>
       <c r="B8" t="n">
-        <v>91910</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510687</v>
+        <v>510842</v>
       </c>
       <c r="R8" t="n">
-        <v>7106478</v>
+        <v>7106609</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128794485</v>
+        <v>128794482</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510780</v>
+        <v>510816</v>
       </c>
       <c r="R9" t="n">
-        <v>7106388</v>
+        <v>7106613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128794479</v>
+        <v>128794483</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510847</v>
+        <v>510704</v>
       </c>
       <c r="R10" t="n">
-        <v>7106602</v>
+        <v>7106576</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128794480</v>
+        <v>128794484</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1598,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510843</v>
+        <v>510684</v>
       </c>
       <c r="R11" t="n">
-        <v>7106605</v>
+        <v>7106476</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128794501</v>
+        <v>128794485</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511349</v>
+        <v>510780</v>
       </c>
       <c r="R12" t="n">
-        <v>7106644</v>
+        <v>7106388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128794506</v>
+        <v>128794486</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510758</v>
+        <v>510777</v>
       </c>
       <c r="R13" t="n">
-        <v>7106421</v>
+        <v>7106379</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128794509</v>
+        <v>128794510</v>
       </c>
       <c r="B14" t="n">
-        <v>91536</v>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510663</v>
+        <v>510841</v>
       </c>
       <c r="R14" t="n">
-        <v>7106445</v>
+        <v>7106597</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128794482</v>
+        <v>128794497</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510816</v>
+        <v>510812</v>
       </c>
       <c r="R15" t="n">
-        <v>7106613</v>
+        <v>7106615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128794481</v>
+        <v>128794476</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>92281</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510842</v>
+        <v>510782</v>
       </c>
       <c r="R16" t="n">
-        <v>7106609</v>
+        <v>7106391</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2125,8 +2110,9 @@
         <v>0</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2145,32 +2131,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128794478</v>
+        <v>128794477</v>
       </c>
       <c r="B17" t="n">
-        <v>91540</v>
+        <v>92281</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511159</v>
+        <v>510687</v>
       </c>
       <c r="R17" t="n">
-        <v>7106615</v>
+        <v>7106478</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,10 +2228,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128794524</v>
+        <v>128794496</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2253,21 +2239,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510700</v>
+        <v>511485</v>
       </c>
       <c r="R18" t="n">
-        <v>7106468</v>
+        <v>7106629</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2313,11 +2299,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,32 +2325,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128794488</v>
+        <v>128794516</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510695</v>
+        <v>511210</v>
       </c>
       <c r="R19" t="n">
-        <v>7106401</v>
+        <v>7106268</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2419,7 +2400,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,32 +2427,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128794491</v>
+        <v>128794517</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2462,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510658</v>
+        <v>511489</v>
       </c>
       <c r="R20" t="n">
-        <v>7106454</v>
+        <v>7106495</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2521,7 +2502,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,32 +2529,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128794496</v>
+        <v>128794518</v>
       </c>
       <c r="B21" t="n">
-        <v>80147</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2583,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>511485</v>
+        <v>511516</v>
       </c>
       <c r="R21" t="n">
-        <v>7106629</v>
+        <v>7106584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,6 +2600,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,32 +2631,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128794498</v>
+        <v>128794519</v>
       </c>
       <c r="B22" t="n">
-        <v>91837</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510780</v>
+        <v>511436</v>
       </c>
       <c r="R22" t="n">
-        <v>7106391</v>
+        <v>7106614</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,6 +2702,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,10 +2733,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128794476</v>
+        <v>128794520</v>
       </c>
       <c r="B23" t="n">
-        <v>91910</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2744,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2062</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510782</v>
+        <v>511309</v>
       </c>
       <c r="R23" t="n">
-        <v>7106391</v>
+        <v>7106636</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,9 +2810,8 @@
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2840,32 +2830,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128794525</v>
+        <v>128794521</v>
       </c>
       <c r="B24" t="n">
-        <v>88940</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2875,10 +2865,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510696</v>
+        <v>511134</v>
       </c>
       <c r="R24" t="n">
-        <v>7106461</v>
+        <v>7106628</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,6 +2901,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2937,32 +2932,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128794515</v>
+        <v>128794522</v>
       </c>
       <c r="B25" t="n">
-        <v>91558</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2972,10 +2967,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511143</v>
+        <v>510692</v>
       </c>
       <c r="R25" t="n">
-        <v>7106625</v>
+        <v>7106564</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,6 +3003,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3034,14 +3034,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128794517</v>
+        <v>128794523</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>511489</v>
+        <v>510685</v>
       </c>
       <c r="R26" t="n">
-        <v>7106495</v>
+        <v>7106500</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,11 +3105,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3136,32 +3131,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128794503</v>
+        <v>128794524</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3171,10 +3166,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510694</v>
+        <v>510700</v>
       </c>
       <c r="R27" t="n">
-        <v>7106493</v>
+        <v>7106468</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,6 +3202,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Granska rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128794486</v>
+        <v>128794499</v>
       </c>
       <c r="B28" t="n">
-        <v>91540</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>510777</v>
+        <v>511149</v>
       </c>
       <c r="R28" t="n">
-        <v>7106379</v>
+        <v>7106300</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128794511</v>
+        <v>128794500</v>
       </c>
       <c r="B29" t="n">
-        <v>91558</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>511450</v>
+        <v>511491</v>
       </c>
       <c r="R29" t="n">
-        <v>7106469</v>
+        <v>7106660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128794516</v>
+        <v>128794501</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3438,21 +3438,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>511210</v>
+        <v>511349</v>
       </c>
       <c r="R30" t="n">
-        <v>7106268</v>
+        <v>7106644</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,11 +3498,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3532,7 +3527,7 @@
         <v>128794502</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3626,32 +3621,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128794497</v>
+        <v>128794503</v>
       </c>
       <c r="B32" t="n">
-        <v>91992</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3661,10 +3656,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>510812</v>
+        <v>510694</v>
       </c>
       <c r="R32" t="n">
-        <v>7106615</v>
+        <v>7106493</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3723,10 +3718,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128794521</v>
+        <v>128794504</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3734,21 +3729,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3758,10 +3753,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>511134</v>
+        <v>510707</v>
       </c>
       <c r="R33" t="n">
-        <v>7106628</v>
+        <v>7106493</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,11 +3789,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3828,7 +3818,7 @@
         <v>128794505</v>
       </c>
       <c r="B34" t="n">
-        <v>80146</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3922,10 +3912,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128794489</v>
+        <v>128794506</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3933,21 +3923,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3957,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>510914</v>
+        <v>510758</v>
       </c>
       <c r="R35" t="n">
-        <v>7106330</v>
+        <v>7106421</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,11 +3983,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4024,10 +4009,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128794504</v>
+        <v>128794507</v>
       </c>
       <c r="B36" t="n">
-        <v>80146</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4059,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>510707</v>
+        <v>510771</v>
       </c>
       <c r="R36" t="n">
-        <v>7106493</v>
+        <v>7106380</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4121,10 +4106,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128794495</v>
+        <v>128794508</v>
       </c>
       <c r="B37" t="n">
-        <v>57724</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4132,42 +4117,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stortjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>510696</v>
+        <v>510782</v>
       </c>
       <c r="R37" t="n">
-        <v>7106472</v>
+        <v>7106356</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4204,14 +4181,14 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Gamla bohål i björk</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -4231,45 +4208,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128794500</v>
+        <v>128794495</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stortjärnhöjden, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>511491</v>
+        <v>510696</v>
       </c>
       <c r="R38" t="n">
-        <v>7106660</v>
+        <v>7106472</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,11 +4289,16 @@
           <t>2025-09-29</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gamla bohål i björk</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG38" t="b">
         <v>0</v>
@@ -4328,10 +4318,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128794513</v>
+        <v>128794488</v>
       </c>
       <c r="B39" t="n">
-        <v>91558</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,21 +4329,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4363,10 +4353,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>511247</v>
+        <v>510695</v>
       </c>
       <c r="R39" t="n">
-        <v>7106612</v>
+        <v>7106401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4399,6 +4389,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4425,10 +4420,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128794523</v>
+        <v>128794489</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4436,21 +4431,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4460,10 +4455,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>510685</v>
+        <v>510914</v>
       </c>
       <c r="R40" t="n">
-        <v>7106500</v>
+        <v>7106330</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4496,6 +4491,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4522,10 +4522,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128794484</v>
+        <v>128794491</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4533,21 +4533,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>510684</v>
+        <v>510658</v>
       </c>
       <c r="R41" t="n">
-        <v>7106476</v>
+        <v>7106454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4593,6 +4593,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4619,10 +4624,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128794510</v>
+        <v>128794492</v>
       </c>
       <c r="B42" t="n">
-        <v>91554</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4630,21 +4635,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4654,10 +4659,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>510841</v>
+        <v>510773</v>
       </c>
       <c r="R42" t="n">
-        <v>7106597</v>
+        <v>7106391</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4690,6 +4695,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4716,32 +4726,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128794512</v>
+        <v>128794526</v>
       </c>
       <c r="B43" t="n">
-        <v>91558</v>
+        <v>89870</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>236437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4751,10 +4761,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>511307</v>
+        <v>510763</v>
       </c>
       <c r="R43" t="n">
-        <v>7106634</v>
+        <v>7106387</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4810,103 +4820,6 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>128794526</v>
-      </c>
-      <c r="B44" t="n">
-        <v>89518</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>236437</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Brun klibbskivling</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Limacella glioderma</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Fr.) Maire</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Stortjärnhöjden, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>510763</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7106387</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Ström</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7126-2026 artfynd.xlsx
+++ b/artfynd/A 7126-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794525</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794509</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794478</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794479</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794480</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794481</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794482</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794483</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794484</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794485</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794486</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794510</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794497</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794476</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794477</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794496</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2424,6 +2514,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794516</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2526,6 +2621,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794517</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2628,6 +2728,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794518</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2730,6 +2835,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794519</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2827,6 +2937,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794520</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2929,6 +3044,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794521</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3031,6 +3151,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794522</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3128,6 +3253,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794523</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3230,6 +3360,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794524</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3327,6 +3462,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794499</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3424,6 +3564,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794500</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3521,6 +3666,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794501</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3618,6 +3768,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794502</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3715,6 +3870,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794503</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3812,6 +3972,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794504</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3909,6 +4074,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794505</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4006,6 +4176,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794506</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4103,6 +4278,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794507</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4205,6 +4385,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794508</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4315,6 +4500,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794495</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4417,6 +4607,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794488</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4519,6 +4714,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794489</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4621,6 +4821,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794491</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4723,6 +4928,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794492</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4820,8 +5030,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>